--- a/Result/profitability/2505.xlsx
+++ b/Result/profitability/2505.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.22</v>
       </c>
       <c r="M2" t="n">
-        <v>0.37375</v>
+        <v>0.38</v>
       </c>
       <c r="N2" t="n">
-        <v>33.58750000000001</v>
+        <v>31.58875</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.04</v>
       </c>
       <c r="M3" t="n">
-        <v>0.36625</v>
+        <v>0.3675</v>
       </c>
       <c r="N3" t="n">
-        <v>30.22875000000001</v>
+        <v>29.20000000000001</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>-0.01</v>
       </c>
       <c r="M4" t="n">
-        <v>0.3475</v>
+        <v>0.29875</v>
       </c>
       <c r="N4" t="n">
-        <v>26.10250000000001</v>
+        <v>26.32500000000001</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>0.13</v>
       </c>
       <c r="M5" t="n">
-        <v>0.29625</v>
+        <v>0.295</v>
       </c>
       <c r="N5" t="n">
-        <v>24.25875000000001</v>
+        <v>25.27500000000001</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>-0.17</v>
       </c>
       <c r="M6" t="n">
-        <v>0.255</v>
+        <v>0.16875</v>
       </c>
       <c r="N6" t="n">
-        <v>21.85500000000001</v>
+        <v>22.93375000000001</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>-0.4</v>
       </c>
       <c r="M7" t="n">
-        <v>0.09999999999999998</v>
+        <v>0.01625</v>
       </c>
       <c r="N7" t="n">
-        <v>17.64875000000001</v>
+        <v>19.0425</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>-0.14</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.02</v>
+        <v>-0.0225</v>
       </c>
       <c r="N8" t="n">
-        <v>14.70000000000001</v>
+        <v>15.94125000000001</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1518,7 +1518,7 @@
         <v>-0.11</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.05500000000000001</v>
+        <v>-0.055</v>
       </c>
       <c r="N9" t="n">
         <v>13.01000000000001</v>
@@ -9830,6 +9830,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2505</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>176</v>
+      </c>
+      <c r="D75" t="n">
+        <v>111</v>
+      </c>
+      <c r="E75" t="n">
+        <v>65</v>
+      </c>
+      <c r="F75" t="n">
+        <v>36.86</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-10</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-5.72%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>60</v>
+      </c>
+      <c r="J75" t="n">
+        <v>50</v>
+      </c>
+      <c r="K75" t="n">
+        <v>55</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.365</v>
+      </c>
+      <c r="N75" t="n">
+        <v>34.93500000000001</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.02000000000000002</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-0.1176470588235295</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>9.93</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.3687337541774973</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>-0.01000000000000001</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-0.0625</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>8.129999999999999</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.282979463974939</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
